--- a/apps/api/assets/vocabulary/小学/人教版/六年级下.xlsx
+++ b/apps/api/assets/vocabulary/小学/人教版/六年级下.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D93"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -1052,6 +1052,16 @@
           <t>watched</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t>vt. 观察；注视；看守；警戒
@@ -1087,6 +1097,16 @@
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>had a cold</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1582,6 +1602,16 @@
           <t>went camping</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -1617,6 +1647,16 @@
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>went fishing</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -1724,6 +1764,16 @@
           <t>took pictures</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
           <t>vbl.照像,摄影</t>
@@ -1832,6 +1882,16 @@
           <t>Labour Day</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (五一国际)劳动节
@@ -1866,6 +1926,16 @@
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Turpan</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2172,6 +2242,16 @@
           <t>go cycling</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 去骑自行车；去骑车；去骑单车</t>
@@ -2277,6 +2357,16 @@
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>look up</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
